--- a/artfynd/A 38070-2024 artfynd.xlsx
+++ b/artfynd/A 38070-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120315882</v>
+        <v>120315890</v>
       </c>
       <c r="B2" t="n">
-        <v>79608</v>
+        <v>57473</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376978</v>
+        <v>376945</v>
       </c>
       <c r="R2" t="n">
-        <v>6928734</v>
+        <v>6928689</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,18 +765,12 @@
           <t>2024-10-09</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flera fynd i området</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,7 +792,7 @@
         <v>120315887</v>
       </c>
       <c r="B3" t="n">
-        <v>57421</v>
+        <v>57431</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -905,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120315890</v>
+        <v>120315862</v>
       </c>
       <c r="B4" t="n">
-        <v>57463</v>
+        <v>74654</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,35 +924,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376945</v>
+        <v>377126</v>
       </c>
       <c r="R4" t="n">
-        <v>6928689</v>
+        <v>6928838</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,6 +995,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1019,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120315862</v>
+        <v>120315882</v>
       </c>
       <c r="B5" t="n">
-        <v>74638</v>
+        <v>79624</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1030,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1062,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377126</v>
+        <v>376978</v>
       </c>
       <c r="R5" t="n">
-        <v>6928838</v>
+        <v>6928734</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,6 +1093,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flera fynd i området</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 38070-2024 artfynd.xlsx
+++ b/artfynd/A 38070-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120315890</v>
+        <v>120315887</v>
       </c>
       <c r="B2" t="n">
-        <v>57473</v>
+        <v>57431</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -763,6 +763,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Förekom i området under hela besöket</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120315887</v>
+        <v>120315862</v>
       </c>
       <c r="B3" t="n">
-        <v>57431</v>
+        <v>74654</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,39 +806,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376945</v>
+        <v>377126</v>
       </c>
       <c r="R3" t="n">
-        <v>6928689</v>
+        <v>6928838</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,17 +875,13 @@
           <t>2024-10-09</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Förekom i området under hela besöket</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -908,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120315862</v>
+        <v>120315882</v>
       </c>
       <c r="B4" t="n">
-        <v>74654</v>
+        <v>79624</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>377126</v>
+        <v>376978</v>
       </c>
       <c r="R4" t="n">
-        <v>6928838</v>
+        <v>6928734</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,6 +979,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera fynd i området</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120315882</v>
+        <v>120315890</v>
       </c>
       <c r="B5" t="n">
-        <v>79624</v>
+        <v>57473</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,26 +1027,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1057,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>376978</v>
+        <v>376945</v>
       </c>
       <c r="R5" t="n">
-        <v>6928734</v>
+        <v>6928689</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,18 +1101,12 @@
           <t>2024-10-09</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flera fynd i området</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38070-2024 artfynd.xlsx
+++ b/artfynd/A 38070-2024 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120315862</v>
+        <v>120315882</v>
       </c>
       <c r="B3" t="n">
-        <v>74654</v>
+        <v>79624</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>377126</v>
+        <v>376978</v>
       </c>
       <c r="R3" t="n">
-        <v>6928838</v>
+        <v>6928734</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,6 +873,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera fynd i området</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120315882</v>
+        <v>120315890</v>
       </c>
       <c r="B4" t="n">
-        <v>79624</v>
+        <v>57473</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,26 +921,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376978</v>
+        <v>376945</v>
       </c>
       <c r="R4" t="n">
-        <v>6928734</v>
+        <v>6928689</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,18 +995,12 @@
           <t>2024-10-09</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flera fynd i området</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120315890</v>
+        <v>120315862</v>
       </c>
       <c r="B5" t="n">
-        <v>57473</v>
+        <v>74654</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,35 +1035,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1063,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>376945</v>
+        <v>377126</v>
       </c>
       <c r="R5" t="n">
-        <v>6928689</v>
+        <v>6928838</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,6 +1106,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38070-2024 artfynd.xlsx
+++ b/artfynd/A 38070-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1123,6 +1123,3071 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120461318</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78543</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>376890</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6928691</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120460548</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>377036</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6928731</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120460108</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>377042</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6928821</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120460591</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>377037</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6928708</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120460059</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57431</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>376993</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6928790</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120460968</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>376968</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6928679</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120460682</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>377016</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6928699</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120459652</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>376947</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6928818</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120460454</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>377022</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6928777</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120460074</v>
+      </c>
+      <c r="B15" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>376993</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6928790</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120460066</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78543</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>377009</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6928804</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120459601</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>376916</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6928831</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120460958</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90594</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>376968</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6928679</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120459810</v>
+      </c>
+      <c r="B19" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>376967</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6928836</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bohål i högstubbe.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120460025</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90594</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>377000</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6928813</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120461047</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>376936</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6928683</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120460235</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>377043</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6928804</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120460504</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>377016</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6928760</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120459553</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>376934</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6928841</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120459943</v>
+      </c>
+      <c r="B25" t="n">
+        <v>77489</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>314</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vitskaftad svartspik</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis viridialba</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>377000</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6928829</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120460726</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>377004</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6928702</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120460451</v>
+      </c>
+      <c r="B27" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>377022</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6928777</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120460909</v>
+      </c>
+      <c r="B28" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>376990</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6928722</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120460956</v>
+      </c>
+      <c r="B29" t="n">
+        <v>90864</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>658</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>376968</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6928679</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120459984</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>376999</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6928819</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120460637</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>377053</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6928774</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120460102</v>
+      </c>
+      <c r="B32" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>377004</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6928780</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120461035</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79652</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>376936</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6928683</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120460124</v>
+      </c>
+      <c r="B34" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>377026</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6928790</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120460931</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>376983</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6928691</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38070-2024 artfynd.xlsx
+++ b/artfynd/A 38070-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120315887</v>
+        <v>120315862</v>
       </c>
       <c r="B2" t="n">
-        <v>57431</v>
+        <v>74654</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376945</v>
+        <v>377126</v>
       </c>
       <c r="R2" t="n">
-        <v>6928689</v>
+        <v>6928838</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,17 +756,13 @@
           <t>2024-10-09</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Förekom i området under hela besöket</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120315882</v>
+        <v>120315887</v>
       </c>
       <c r="B3" t="n">
-        <v>79624</v>
+        <v>57431</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,30 +793,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376978</v>
+        <v>376945</v>
       </c>
       <c r="R3" t="n">
-        <v>6928734</v>
+        <v>6928689</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +873,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flera fynd i området</t>
+          <t>Förekom i området under hela besöket</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1019,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120315862</v>
+        <v>120315882</v>
       </c>
       <c r="B5" t="n">
-        <v>74654</v>
+        <v>79624</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1030,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1062,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377126</v>
+        <v>376978</v>
       </c>
       <c r="R5" t="n">
-        <v>6928838</v>
+        <v>6928734</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,6 +1093,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flera fynd i området</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,7 +1125,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120461318</v>
+        <v>120460066</v>
       </c>
       <c r="B6" t="n">
         <v>78543</v>
@@ -1165,13 +1165,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>376890</v>
+        <v>377009</v>
       </c>
       <c r="R6" t="n">
-        <v>6928691</v>
+        <v>6928804</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120460548</v>
+        <v>120460569</v>
       </c>
       <c r="B7" t="n">
         <v>79624</v>
@@ -1329,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120460108</v>
+        <v>120460958</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,37 +1345,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>377042</v>
+        <v>376968</v>
       </c>
       <c r="R8" t="n">
-        <v>6928821</v>
+        <v>6928679</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1419,19 +1419,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120460591</v>
+        <v>120460968</v>
       </c>
       <c r="B9" t="n">
         <v>79624</v>
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>377037</v>
+        <v>376968</v>
       </c>
       <c r="R9" t="n">
-        <v>6928708</v>
+        <v>6928679</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120460059</v>
+        <v>120461318</v>
       </c>
       <c r="B10" t="n">
-        <v>57431</v>
+        <v>78543</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,41 +1545,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>230405</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>376993</v>
+        <v>376890</v>
       </c>
       <c r="R10" t="n">
-        <v>6928790</v>
+        <v>6928691</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1623,22 +1623,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120460968</v>
+        <v>120460059</v>
       </c>
       <c r="B11" t="n">
-        <v>79624</v>
+        <v>57431</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,25 +1647,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>376968</v>
+        <v>376993</v>
       </c>
       <c r="R11" t="n">
-        <v>6928679</v>
+        <v>6928790</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1737,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120460682</v>
+        <v>120460956</v>
       </c>
       <c r="B12" t="n">
-        <v>79624</v>
+        <v>90864</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,37 +1753,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>377016</v>
+        <v>376968</v>
       </c>
       <c r="R12" t="n">
-        <v>6928699</v>
+        <v>6928679</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1827,22 +1827,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120459652</v>
+        <v>120460025</v>
       </c>
       <c r="B13" t="n">
-        <v>79624</v>
+        <v>90594</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>376947</v>
+        <v>377000</v>
       </c>
       <c r="R13" t="n">
-        <v>6928818</v>
+        <v>6928813</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120460454</v>
+        <v>120459810</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1957,37 +1957,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>377022</v>
+        <v>376967</v>
       </c>
       <c r="R14" t="n">
-        <v>6928777</v>
+        <v>6928836</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2017,6 +2017,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Bohål i högstubbe.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2031,22 +2036,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120460074</v>
+        <v>120459984</v>
       </c>
       <c r="B15" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2059,37 +2064,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>376993</v>
+        <v>376999</v>
       </c>
       <c r="R15" t="n">
-        <v>6928790</v>
+        <v>6928819</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2133,22 +2138,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120460066</v>
+        <v>120460931</v>
       </c>
       <c r="B16" t="n">
-        <v>78543</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2161,16 +2166,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2181,17 +2186,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>377009</v>
+        <v>376983</v>
       </c>
       <c r="R16" t="n">
-        <v>6928804</v>
+        <v>6928691</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2235,22 +2240,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120459601</v>
+        <v>120459652</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,37 +2268,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>376916</v>
+        <v>376947</v>
       </c>
       <c r="R17" t="n">
-        <v>6928831</v>
+        <v>6928818</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2337,22 +2342,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120460958</v>
+        <v>120460451</v>
       </c>
       <c r="B18" t="n">
-        <v>90594</v>
+        <v>74654</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2365,21 +2370,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2389,10 +2394,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>376968</v>
+        <v>377022</v>
       </c>
       <c r="R18" t="n">
-        <v>6928679</v>
+        <v>6928777</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2451,10 +2456,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120459810</v>
+        <v>120459943</v>
       </c>
       <c r="B19" t="n">
-        <v>90598</v>
+        <v>77489</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2467,37 +2472,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>376967</v>
+        <v>377000</v>
       </c>
       <c r="R19" t="n">
-        <v>6928836</v>
+        <v>6928829</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2527,11 +2532,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Bohål i högstubbe.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2546,22 +2546,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120460025</v>
+        <v>120460102</v>
       </c>
       <c r="B20" t="n">
-        <v>90594</v>
+        <v>74654</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2574,21 +2574,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>377000</v>
+        <v>377004</v>
       </c>
       <c r="R20" t="n">
-        <v>6928813</v>
+        <v>6928780</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2660,10 +2660,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120461047</v>
+        <v>120460909</v>
       </c>
       <c r="B21" t="n">
-        <v>79624</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2676,21 +2676,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2700,10 +2700,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>376936</v>
+        <v>376990</v>
       </c>
       <c r="R21" t="n">
-        <v>6928683</v>
+        <v>6928722</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2762,7 +2762,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120460235</v>
+        <v>120459553</v>
       </c>
       <c r="B22" t="n">
         <v>78542</v>
@@ -2798,17 +2798,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>377043</v>
+        <v>376934</v>
       </c>
       <c r="R22" t="n">
-        <v>6928804</v>
+        <v>6928841</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2852,19 +2852,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120460504</v>
+        <v>120461047</v>
       </c>
       <c r="B23" t="n">
         <v>79624</v>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>377016</v>
+        <v>376936</v>
       </c>
       <c r="R23" t="n">
-        <v>6928760</v>
+        <v>6928683</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2966,10 +2966,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120459553</v>
+        <v>120460074</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2982,21 +2982,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3006,13 +3006,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>376934</v>
+        <v>376993</v>
       </c>
       <c r="R24" t="n">
-        <v>6928841</v>
+        <v>6928790</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3068,10 +3068,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120459943</v>
+        <v>120460124</v>
       </c>
       <c r="B25" t="n">
-        <v>77489</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3084,21 +3084,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>314</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>377000</v>
+        <v>377026</v>
       </c>
       <c r="R25" t="n">
-        <v>6928829</v>
+        <v>6928790</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3170,10 +3170,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120460726</v>
+        <v>120460235</v>
       </c>
       <c r="B26" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3186,21 +3186,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3210,13 +3210,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>377004</v>
+        <v>377043</v>
       </c>
       <c r="R26" t="n">
-        <v>6928702</v>
+        <v>6928804</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3272,10 +3272,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120460451</v>
+        <v>120460454</v>
       </c>
       <c r="B27" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3288,21 +3288,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3374,10 +3374,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120460909</v>
+        <v>120460682</v>
       </c>
       <c r="B28" t="n">
-        <v>90580</v>
+        <v>79624</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3390,37 +3390,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>376990</v>
+        <v>377016</v>
       </c>
       <c r="R28" t="n">
-        <v>6928722</v>
+        <v>6928699</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3464,22 +3464,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120460956</v>
+        <v>120460726</v>
       </c>
       <c r="B29" t="n">
-        <v>90864</v>
+        <v>79624</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3492,37 +3492,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>376968</v>
+        <v>377004</v>
       </c>
       <c r="R29" t="n">
-        <v>6928679</v>
+        <v>6928702</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3566,22 +3566,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120459984</v>
+        <v>120460637</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3594,21 +3594,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3618,13 +3618,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>376999</v>
+        <v>377053</v>
       </c>
       <c r="R30" t="n">
-        <v>6928819</v>
+        <v>6928774</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3680,10 +3680,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120460637</v>
+        <v>120460108</v>
       </c>
       <c r="B31" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3696,21 +3696,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3720,13 +3720,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>377053</v>
+        <v>377042</v>
       </c>
       <c r="R31" t="n">
-        <v>6928774</v>
+        <v>6928821</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3782,10 +3782,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120460102</v>
+        <v>120460504</v>
       </c>
       <c r="B32" t="n">
-        <v>74654</v>
+        <v>79624</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3798,21 +3798,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3822,10 +3822,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>377004</v>
+        <v>377016</v>
       </c>
       <c r="R32" t="n">
-        <v>6928780</v>
+        <v>6928760</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120461035</v>
+        <v>120459601</v>
       </c>
       <c r="B33" t="n">
-        <v>79652</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3896,41 +3896,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>376936</v>
+        <v>376916</v>
       </c>
       <c r="R33" t="n">
-        <v>6928683</v>
+        <v>6928831</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3974,22 +3974,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120460124</v>
+        <v>120461035</v>
       </c>
       <c r="B34" t="n">
-        <v>90580</v>
+        <v>79652</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3998,25 +3998,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4026,10 +4026,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>377026</v>
+        <v>376936</v>
       </c>
       <c r="R34" t="n">
-        <v>6928790</v>
+        <v>6928683</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4088,10 +4088,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120460931</v>
+        <v>120460591</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4104,21 +4104,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>376983</v>
+        <v>377037</v>
       </c>
       <c r="R35" t="n">
-        <v>6928691</v>
+        <v>6928708</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 38070-2024 artfynd.xlsx
+++ b/artfynd/A 38070-2024 artfynd.xlsx
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120315890</v>
+        <v>120315882</v>
       </c>
       <c r="B4" t="n">
-        <v>57473</v>
+        <v>79624</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,35 +916,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376945</v>
+        <v>376978</v>
       </c>
       <c r="R4" t="n">
-        <v>6928689</v>
+        <v>6928734</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,12 +981,18 @@
           <t>2024-10-09</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera fynd i området</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1014,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120315882</v>
+        <v>120315890</v>
       </c>
       <c r="B5" t="n">
-        <v>79624</v>
+        <v>57473</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,26 +1027,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1057,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>376978</v>
+        <v>376945</v>
       </c>
       <c r="R5" t="n">
-        <v>6928734</v>
+        <v>6928689</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,18 +1101,12 @@
           <t>2024-10-09</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flera fynd i området</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1227,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120460569</v>
+        <v>120460074</v>
       </c>
       <c r="B7" t="n">
-        <v>79624</v>
+        <v>74654</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,21 +1243,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>377036</v>
+        <v>376993</v>
       </c>
       <c r="R7" t="n">
-        <v>6928731</v>
+        <v>6928790</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120460958</v>
+        <v>120460637</v>
       </c>
       <c r="B8" t="n">
-        <v>90594</v>
+        <v>79624</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,37 +1345,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>376968</v>
+        <v>377053</v>
       </c>
       <c r="R8" t="n">
-        <v>6928679</v>
+        <v>6928774</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1419,22 +1419,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120460968</v>
+        <v>120460451</v>
       </c>
       <c r="B9" t="n">
-        <v>79624</v>
+        <v>74654</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,21 +1447,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>376968</v>
+        <v>377022</v>
       </c>
       <c r="R9" t="n">
-        <v>6928679</v>
+        <v>6928777</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120461318</v>
+        <v>120460956</v>
       </c>
       <c r="B10" t="n">
-        <v>78543</v>
+        <v>90864</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,37 +1549,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>230405</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>376890</v>
+        <v>376968</v>
       </c>
       <c r="R10" t="n">
-        <v>6928691</v>
+        <v>6928679</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1623,22 +1623,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120460059</v>
+        <v>120460682</v>
       </c>
       <c r="B11" t="n">
-        <v>57431</v>
+        <v>79624</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,41 +1647,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>376993</v>
+        <v>377016</v>
       </c>
       <c r="R11" t="n">
-        <v>6928790</v>
+        <v>6928699</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1725,22 +1725,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120460956</v>
+        <v>120459943</v>
       </c>
       <c r="B12" t="n">
-        <v>90864</v>
+        <v>77489</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>376968</v>
+        <v>377000</v>
       </c>
       <c r="R12" t="n">
-        <v>6928679</v>
+        <v>6928829</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120459810</v>
+        <v>120460909</v>
       </c>
       <c r="B14" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1957,37 +1957,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>376967</v>
+        <v>376990</v>
       </c>
       <c r="R14" t="n">
-        <v>6928836</v>
+        <v>6928722</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2017,11 +2017,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Bohål i högstubbe.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,19 +2031,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120459984</v>
+        <v>120460454</v>
       </c>
       <c r="B15" t="n">
         <v>78542</v>
@@ -2084,17 +2079,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>376999</v>
+        <v>377022</v>
       </c>
       <c r="R15" t="n">
-        <v>6928819</v>
+        <v>6928777</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2138,19 +2133,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120460931</v>
+        <v>120460235</v>
       </c>
       <c r="B16" t="n">
         <v>78542</v>
@@ -2186,17 +2181,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>376983</v>
+        <v>377043</v>
       </c>
       <c r="R16" t="n">
-        <v>6928691</v>
+        <v>6928804</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2240,22 +2235,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120459652</v>
+        <v>120460102</v>
       </c>
       <c r="B17" t="n">
-        <v>79624</v>
+        <v>74654</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2268,21 +2263,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2292,10 +2287,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>376947</v>
+        <v>377004</v>
       </c>
       <c r="R17" t="n">
-        <v>6928818</v>
+        <v>6928780</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2354,10 +2349,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120460451</v>
+        <v>120460591</v>
       </c>
       <c r="B18" t="n">
-        <v>74654</v>
+        <v>79624</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2370,21 +2365,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2394,10 +2389,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>377022</v>
+        <v>377037</v>
       </c>
       <c r="R18" t="n">
-        <v>6928777</v>
+        <v>6928708</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2456,10 +2451,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120459943</v>
+        <v>120459553</v>
       </c>
       <c r="B19" t="n">
-        <v>77489</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2472,21 +2467,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2496,10 +2491,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>377000</v>
+        <v>376934</v>
       </c>
       <c r="R19" t="n">
-        <v>6928829</v>
+        <v>6928841</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2558,10 +2553,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120460102</v>
+        <v>120460124</v>
       </c>
       <c r="B20" t="n">
-        <v>74654</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2574,21 +2569,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2598,10 +2593,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>377004</v>
+        <v>377026</v>
       </c>
       <c r="R20" t="n">
-        <v>6928780</v>
+        <v>6928790</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2660,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120460909</v>
+        <v>120460968</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>79624</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2676,21 +2671,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2700,10 +2695,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>376990</v>
+        <v>376968</v>
       </c>
       <c r="R21" t="n">
-        <v>6928722</v>
+        <v>6928679</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2762,10 +2757,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120459553</v>
+        <v>120461047</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2778,21 +2773,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2802,10 +2797,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>376934</v>
+        <v>376936</v>
       </c>
       <c r="R22" t="n">
-        <v>6928841</v>
+        <v>6928683</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2864,10 +2859,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120461047</v>
+        <v>120459984</v>
       </c>
       <c r="B23" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2880,37 +2875,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>376936</v>
+        <v>376999</v>
       </c>
       <c r="R23" t="n">
-        <v>6928683</v>
+        <v>6928819</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2954,22 +2949,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120460074</v>
+        <v>120459810</v>
       </c>
       <c r="B24" t="n">
-        <v>74654</v>
+        <v>90598</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2982,37 +2977,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>376993</v>
+        <v>376967</v>
       </c>
       <c r="R24" t="n">
-        <v>6928790</v>
+        <v>6928836</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3042,6 +3037,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Bohål i högstubbe.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3056,22 +3056,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120460124</v>
+        <v>120460108</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3084,37 +3084,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>377026</v>
+        <v>377042</v>
       </c>
       <c r="R25" t="n">
-        <v>6928790</v>
+        <v>6928821</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3158,22 +3158,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120460235</v>
+        <v>120460726</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3186,21 +3186,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3210,13 +3210,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>377043</v>
+        <v>377004</v>
       </c>
       <c r="R26" t="n">
-        <v>6928804</v>
+        <v>6928702</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3272,10 +3272,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120460454</v>
+        <v>120461035</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3284,25 +3284,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3312,10 +3312,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>377022</v>
+        <v>376936</v>
       </c>
       <c r="R27" t="n">
-        <v>6928777</v>
+        <v>6928683</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3374,10 +3374,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120460682</v>
+        <v>120460958</v>
       </c>
       <c r="B28" t="n">
-        <v>79624</v>
+        <v>90594</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3390,37 +3390,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>377016</v>
+        <v>376968</v>
       </c>
       <c r="R28" t="n">
-        <v>6928699</v>
+        <v>6928679</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3464,19 +3464,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120460726</v>
+        <v>120460569</v>
       </c>
       <c r="B29" t="n">
         <v>79624</v>
@@ -3512,17 +3512,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>377004</v>
+        <v>377036</v>
       </c>
       <c r="R29" t="n">
-        <v>6928702</v>
+        <v>6928731</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3566,19 +3566,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120460637</v>
+        <v>120459652</v>
       </c>
       <c r="B30" t="n">
         <v>79624</v>
@@ -3614,17 +3614,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>377053</v>
+        <v>376947</v>
       </c>
       <c r="R30" t="n">
-        <v>6928774</v>
+        <v>6928818</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3668,22 +3668,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120460108</v>
+        <v>120460059</v>
       </c>
       <c r="B31" t="n">
-        <v>78542</v>
+        <v>57431</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3692,41 +3692,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>377042</v>
+        <v>376993</v>
       </c>
       <c r="R31" t="n">
-        <v>6928821</v>
+        <v>6928790</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3770,12 +3770,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120459601</v>
+        <v>120461318</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>78543</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3900,16 +3900,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>376916</v>
+        <v>376890</v>
       </c>
       <c r="R33" t="n">
-        <v>6928831</v>
+        <v>6928691</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -3986,10 +3986,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120461035</v>
+        <v>120460931</v>
       </c>
       <c r="B34" t="n">
-        <v>79652</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3998,25 +3998,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4026,10 +4026,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>376936</v>
+        <v>376983</v>
       </c>
       <c r="R34" t="n">
-        <v>6928683</v>
+        <v>6928691</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4088,10 +4088,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120460591</v>
+        <v>120459601</v>
       </c>
       <c r="B35" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4104,37 +4104,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>377037</v>
+        <v>376916</v>
       </c>
       <c r="R35" t="n">
-        <v>6928708</v>
+        <v>6928831</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4178,12 +4178,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 38070-2024 artfynd.xlsx
+++ b/artfynd/A 38070-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120315862</v>
+        <v>120315882</v>
       </c>
       <c r="B2" t="n">
-        <v>74654</v>
+        <v>79624</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>377126</v>
+        <v>376978</v>
       </c>
       <c r="R2" t="n">
-        <v>6928838</v>
+        <v>6928734</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +754,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flera fynd i området</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120315887</v>
+        <v>120315890</v>
       </c>
       <c r="B3" t="n">
-        <v>57431</v>
+        <v>57473</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +798,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -869,11 +874,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Förekom i området under hela besöket</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120315882</v>
+        <v>120315887</v>
       </c>
       <c r="B4" t="n">
-        <v>79624</v>
+        <v>57431</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,30 +912,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376978</v>
+        <v>376945</v>
       </c>
       <c r="R4" t="n">
-        <v>6928734</v>
+        <v>6928689</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +992,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flera fynd i området</t>
+          <t>Förekom i området under hela besöket</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,7 +1001,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120315890</v>
+        <v>120315862</v>
       </c>
       <c r="B5" t="n">
-        <v>57473</v>
+        <v>74654</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,35 +1035,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1063,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>376945</v>
+        <v>377126</v>
       </c>
       <c r="R5" t="n">
-        <v>6928689</v>
+        <v>6928838</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,6 +1106,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120460066</v>
+        <v>120460235</v>
       </c>
       <c r="B6" t="n">
-        <v>78543</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,16 +1141,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1165,13 +1165,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>377009</v>
+        <v>377043</v>
       </c>
       <c r="R6" t="n">
         <v>6928804</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120460074</v>
+        <v>120460682</v>
       </c>
       <c r="B7" t="n">
-        <v>74654</v>
+        <v>79624</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,37 +1243,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>376993</v>
+        <v>377016</v>
       </c>
       <c r="R7" t="n">
-        <v>6928790</v>
+        <v>6928699</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,12 +1317,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1431,10 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120460451</v>
+        <v>120461047</v>
       </c>
       <c r="B9" t="n">
-        <v>74654</v>
+        <v>79624</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,21 +1447,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>377022</v>
+        <v>376936</v>
       </c>
       <c r="R9" t="n">
-        <v>6928777</v>
+        <v>6928683</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120460956</v>
+        <v>120460124</v>
       </c>
       <c r="B10" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,21 +1549,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>376968</v>
+        <v>377026</v>
       </c>
       <c r="R10" t="n">
-        <v>6928679</v>
+        <v>6928790</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,10 +1635,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120460682</v>
+        <v>120459984</v>
       </c>
       <c r="B11" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,21 +1651,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>377016</v>
+        <v>376999</v>
       </c>
       <c r="R11" t="n">
-        <v>6928699</v>
+        <v>6928819</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1737,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120459943</v>
+        <v>120461318</v>
       </c>
       <c r="B12" t="n">
-        <v>77489</v>
+        <v>78543</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,37 +1753,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>314</v>
+        <v>230405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>377000</v>
+        <v>376890</v>
       </c>
       <c r="R12" t="n">
-        <v>6928829</v>
+        <v>6928691</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1827,22 +1827,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120460025</v>
+        <v>120459601</v>
       </c>
       <c r="B13" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1855,37 +1855,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>377000</v>
+        <v>376916</v>
       </c>
       <c r="R13" t="n">
-        <v>6928813</v>
+        <v>6928831</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1929,22 +1929,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120460909</v>
+        <v>120460066</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>78543</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1957,37 +1957,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>230405</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>376990</v>
+        <v>377009</v>
       </c>
       <c r="R14" t="n">
-        <v>6928722</v>
+        <v>6928804</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2031,22 +2031,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120460454</v>
+        <v>120460025</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>377022</v>
+        <v>377000</v>
       </c>
       <c r="R15" t="n">
-        <v>6928777</v>
+        <v>6928813</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120460235</v>
+        <v>120460909</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2161,37 +2161,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>377043</v>
+        <v>376990</v>
       </c>
       <c r="R16" t="n">
-        <v>6928804</v>
+        <v>6928722</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2235,22 +2235,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120460102</v>
+        <v>120460059</v>
       </c>
       <c r="B17" t="n">
-        <v>74654</v>
+        <v>57431</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2259,25 +2259,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>377004</v>
+        <v>376993</v>
       </c>
       <c r="R17" t="n">
-        <v>6928780</v>
+        <v>6928790</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2349,10 +2349,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120460591</v>
+        <v>120460956</v>
       </c>
       <c r="B18" t="n">
-        <v>79624</v>
+        <v>90864</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2365,21 +2365,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2389,10 +2389,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>377037</v>
+        <v>376968</v>
       </c>
       <c r="R18" t="n">
-        <v>6928708</v>
+        <v>6928679</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120459553</v>
+        <v>120460931</v>
       </c>
       <c r="B19" t="n">
         <v>78542</v>
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>376934</v>
+        <v>376983</v>
       </c>
       <c r="R19" t="n">
-        <v>6928841</v>
+        <v>6928691</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2553,10 +2553,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120460124</v>
+        <v>120460074</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>74654</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2569,21 +2569,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>377026</v>
+        <v>376993</v>
       </c>
       <c r="R20" t="n">
         <v>6928790</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120460968</v>
+        <v>120459652</v>
       </c>
       <c r="B21" t="n">
         <v>79624</v>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>376968</v>
+        <v>376947</v>
       </c>
       <c r="R21" t="n">
-        <v>6928679</v>
+        <v>6928818</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2757,10 +2757,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120461047</v>
+        <v>120459943</v>
       </c>
       <c r="B22" t="n">
-        <v>79624</v>
+        <v>77489</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2773,21 +2773,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>376936</v>
+        <v>377000</v>
       </c>
       <c r="R22" t="n">
-        <v>6928683</v>
+        <v>6928829</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2859,10 +2859,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120459984</v>
+        <v>120460504</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2875,37 +2875,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>376999</v>
+        <v>377016</v>
       </c>
       <c r="R23" t="n">
-        <v>6928819</v>
+        <v>6928760</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2949,22 +2949,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120459810</v>
+        <v>120460968</v>
       </c>
       <c r="B24" t="n">
-        <v>90598</v>
+        <v>79624</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2977,37 +2977,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>376967</v>
+        <v>376968</v>
       </c>
       <c r="R24" t="n">
-        <v>6928836</v>
+        <v>6928679</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3037,11 +3037,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Bohål i högstubbe.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3056,22 +3051,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120460108</v>
+        <v>120460726</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3084,21 +3079,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3108,13 +3103,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>377042</v>
+        <v>377004</v>
       </c>
       <c r="R25" t="n">
-        <v>6928821</v>
+        <v>6928702</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3170,10 +3165,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120460726</v>
+        <v>120460454</v>
       </c>
       <c r="B26" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3186,37 +3181,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>377004</v>
+        <v>377022</v>
       </c>
       <c r="R26" t="n">
-        <v>6928702</v>
+        <v>6928777</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3260,22 +3255,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120461035</v>
+        <v>120459810</v>
       </c>
       <c r="B27" t="n">
-        <v>79652</v>
+        <v>90598</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3284,41 +3279,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>376936</v>
+        <v>376967</v>
       </c>
       <c r="R27" t="n">
-        <v>6928683</v>
+        <v>6928836</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3348,6 +3343,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Bohål i högstubbe.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3362,22 +3362,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120460958</v>
+        <v>120460591</v>
       </c>
       <c r="B28" t="n">
-        <v>90594</v>
+        <v>79624</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3390,21 +3390,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3414,10 +3414,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>376968</v>
+        <v>377037</v>
       </c>
       <c r="R28" t="n">
-        <v>6928679</v>
+        <v>6928708</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3476,7 +3476,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120460569</v>
+        <v>120460548</v>
       </c>
       <c r="B29" t="n">
         <v>79624</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120459652</v>
+        <v>120460451</v>
       </c>
       <c r="B30" t="n">
-        <v>79624</v>
+        <v>74654</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3594,21 +3594,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>376947</v>
+        <v>377022</v>
       </c>
       <c r="R30" t="n">
-        <v>6928818</v>
+        <v>6928777</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3680,10 +3680,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120460059</v>
+        <v>120459553</v>
       </c>
       <c r="B31" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3692,25 +3692,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3720,13 +3720,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>376993</v>
+        <v>376934</v>
       </c>
       <c r="R31" t="n">
-        <v>6928790</v>
+        <v>6928841</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3782,10 +3782,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120460504</v>
+        <v>120461035</v>
       </c>
       <c r="B32" t="n">
-        <v>79624</v>
+        <v>79652</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3794,25 +3794,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3822,10 +3822,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>377016</v>
+        <v>376936</v>
       </c>
       <c r="R32" t="n">
-        <v>6928760</v>
+        <v>6928683</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120461318</v>
+        <v>120460102</v>
       </c>
       <c r="B33" t="n">
-        <v>78543</v>
+        <v>74654</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3900,37 +3900,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>230405</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>376890</v>
+        <v>377004</v>
       </c>
       <c r="R33" t="n">
-        <v>6928691</v>
+        <v>6928780</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3974,19 +3974,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120460931</v>
+        <v>120460108</v>
       </c>
       <c r="B34" t="n">
         <v>78542</v>
@@ -4022,17 +4022,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>376983</v>
+        <v>377042</v>
       </c>
       <c r="R34" t="n">
-        <v>6928691</v>
+        <v>6928821</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4076,22 +4076,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120459601</v>
+        <v>120460958</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4104,37 +4104,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>376916</v>
+        <v>376968</v>
       </c>
       <c r="R35" t="n">
-        <v>6928831</v>
+        <v>6928679</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4178,12 +4178,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 38070-2024 artfynd.xlsx
+++ b/artfynd/A 38070-2024 artfynd.xlsx
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120315887</v>
+        <v>120315862</v>
       </c>
       <c r="B4" t="n">
-        <v>57431</v>
+        <v>74654</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,39 +912,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376945</v>
+        <v>377126</v>
       </c>
       <c r="R4" t="n">
-        <v>6928689</v>
+        <v>6928838</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,17 +981,13 @@
           <t>2024-10-09</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Förekom i området under hela besöket</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1019,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120315862</v>
+        <v>120315887</v>
       </c>
       <c r="B5" t="n">
-        <v>74654</v>
+        <v>57431</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,30 +1018,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1062,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377126</v>
+        <v>376945</v>
       </c>
       <c r="R5" t="n">
-        <v>6928838</v>
+        <v>6928689</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,13 +1096,17 @@
           <t>2024-10-09</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Förekom i området under hela besöket</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120460235</v>
+        <v>120460591</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,37 +1141,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>377043</v>
+        <v>377037</v>
       </c>
       <c r="R6" t="n">
-        <v>6928804</v>
+        <v>6928708</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,22 +1215,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120460682</v>
+        <v>120459984</v>
       </c>
       <c r="B7" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,21 +1243,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>377016</v>
+        <v>376999</v>
       </c>
       <c r="R7" t="n">
-        <v>6928699</v>
+        <v>6928819</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120460637</v>
+        <v>120460548</v>
       </c>
       <c r="B8" t="n">
         <v>79624</v>
@@ -1365,17 +1365,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>377053</v>
+        <v>377036</v>
       </c>
       <c r="R8" t="n">
-        <v>6928774</v>
+        <v>6928731</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1419,22 +1419,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120461047</v>
+        <v>120459553</v>
       </c>
       <c r="B9" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,21 +1447,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>376936</v>
+        <v>376934</v>
       </c>
       <c r="R9" t="n">
-        <v>6928683</v>
+        <v>6928841</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120460124</v>
+        <v>120460956</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,21 +1549,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>377026</v>
+        <v>376968</v>
       </c>
       <c r="R10" t="n">
-        <v>6928790</v>
+        <v>6928679</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,7 +1635,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120459984</v>
+        <v>120460454</v>
       </c>
       <c r="B11" t="n">
         <v>78542</v>
@@ -1671,17 +1671,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>376999</v>
+        <v>377022</v>
       </c>
       <c r="R11" t="n">
-        <v>6928819</v>
+        <v>6928777</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1725,22 +1725,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120461318</v>
+        <v>120460726</v>
       </c>
       <c r="B12" t="n">
-        <v>78543</v>
+        <v>79624</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230405</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>376890</v>
+        <v>377004</v>
       </c>
       <c r="R12" t="n">
-        <v>6928691</v>
+        <v>6928702</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120459601</v>
+        <v>120460958</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1855,37 +1855,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>376916</v>
+        <v>376968</v>
       </c>
       <c r="R13" t="n">
-        <v>6928831</v>
+        <v>6928679</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1929,22 +1929,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120460066</v>
+        <v>120460074</v>
       </c>
       <c r="B14" t="n">
-        <v>78543</v>
+        <v>74654</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1957,37 +1957,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>230405</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>377009</v>
+        <v>376993</v>
       </c>
       <c r="R14" t="n">
-        <v>6928804</v>
+        <v>6928790</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2031,22 +2031,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120460025</v>
+        <v>120460059</v>
       </c>
       <c r="B15" t="n">
-        <v>90594</v>
+        <v>57431</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2055,25 +2055,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2083,13 +2083,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>377000</v>
+        <v>376993</v>
       </c>
       <c r="R15" t="n">
-        <v>6928813</v>
+        <v>6928790</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120460909</v>
+        <v>120461318</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>78543</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2161,37 +2161,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>230405</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>376990</v>
+        <v>376890</v>
       </c>
       <c r="R16" t="n">
-        <v>6928722</v>
+        <v>6928691</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2235,22 +2235,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120460059</v>
+        <v>120460931</v>
       </c>
       <c r="B17" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2259,25 +2259,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>376993</v>
+        <v>376983</v>
       </c>
       <c r="R17" t="n">
-        <v>6928790</v>
+        <v>6928691</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2349,10 +2349,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120460956</v>
+        <v>120460637</v>
       </c>
       <c r="B18" t="n">
-        <v>90864</v>
+        <v>79624</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2365,37 +2365,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>376968</v>
+        <v>377053</v>
       </c>
       <c r="R18" t="n">
-        <v>6928679</v>
+        <v>6928774</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2439,22 +2439,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120460931</v>
+        <v>120461035</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2463,25 +2463,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>376983</v>
+        <v>376936</v>
       </c>
       <c r="R19" t="n">
-        <v>6928691</v>
+        <v>6928683</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2553,10 +2553,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120460074</v>
+        <v>120460968</v>
       </c>
       <c r="B20" t="n">
-        <v>74654</v>
+        <v>79624</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2569,21 +2569,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>376993</v>
+        <v>376968</v>
       </c>
       <c r="R20" t="n">
-        <v>6928790</v>
+        <v>6928679</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2655,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120459652</v>
+        <v>120460025</v>
       </c>
       <c r="B21" t="n">
-        <v>79624</v>
+        <v>90594</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2671,21 +2671,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>376947</v>
+        <v>377000</v>
       </c>
       <c r="R21" t="n">
-        <v>6928818</v>
+        <v>6928813</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2757,10 +2757,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120459943</v>
+        <v>120460108</v>
       </c>
       <c r="B22" t="n">
-        <v>77489</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2773,37 +2773,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>377000</v>
+        <v>377042</v>
       </c>
       <c r="R22" t="n">
-        <v>6928829</v>
+        <v>6928821</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2847,22 +2847,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120460504</v>
+        <v>120460102</v>
       </c>
       <c r="B23" t="n">
-        <v>79624</v>
+        <v>74654</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2875,21 +2875,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>377016</v>
+        <v>377004</v>
       </c>
       <c r="R23" t="n">
-        <v>6928760</v>
+        <v>6928780</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2961,10 +2961,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120460968</v>
+        <v>120460909</v>
       </c>
       <c r="B24" t="n">
-        <v>79624</v>
+        <v>90580</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2977,21 +2977,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>376968</v>
+        <v>376990</v>
       </c>
       <c r="R24" t="n">
-        <v>6928679</v>
+        <v>6928722</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3063,7 +3063,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120460726</v>
+        <v>120460682</v>
       </c>
       <c r="B25" t="n">
         <v>79624</v>
@@ -3103,13 +3103,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>377004</v>
+        <v>377016</v>
       </c>
       <c r="R25" t="n">
-        <v>6928702</v>
+        <v>6928699</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3165,10 +3165,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120460454</v>
+        <v>120460504</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3181,21 +3181,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3205,10 +3205,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>377022</v>
+        <v>377016</v>
       </c>
       <c r="R26" t="n">
-        <v>6928777</v>
+        <v>6928760</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3267,10 +3267,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120459810</v>
+        <v>120459601</v>
       </c>
       <c r="B27" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3307,13 +3307,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>376967</v>
+        <v>376916</v>
       </c>
       <c r="R27" t="n">
-        <v>6928836</v>
+        <v>6928831</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3343,11 +3343,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Bohål i högstubbe.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3374,10 +3369,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120460591</v>
+        <v>120460235</v>
       </c>
       <c r="B28" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3390,37 +3385,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>377037</v>
+        <v>377043</v>
       </c>
       <c r="R28" t="n">
-        <v>6928708</v>
+        <v>6928804</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3464,22 +3459,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120460548</v>
+        <v>120459943</v>
       </c>
       <c r="B29" t="n">
-        <v>79624</v>
+        <v>77489</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3492,21 +3487,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3516,10 +3511,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>377036</v>
+        <v>377000</v>
       </c>
       <c r="R29" t="n">
-        <v>6928731</v>
+        <v>6928829</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3578,10 +3573,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120460451</v>
+        <v>120460124</v>
       </c>
       <c r="B30" t="n">
-        <v>74654</v>
+        <v>90580</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3594,21 +3589,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3618,10 +3613,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>377022</v>
+        <v>377026</v>
       </c>
       <c r="R30" t="n">
-        <v>6928777</v>
+        <v>6928790</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3680,10 +3675,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120459553</v>
+        <v>120459652</v>
       </c>
       <c r="B31" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3696,21 +3691,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3720,10 +3715,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>376934</v>
+        <v>376947</v>
       </c>
       <c r="R31" t="n">
-        <v>6928841</v>
+        <v>6928818</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3782,10 +3777,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120461035</v>
+        <v>120459810</v>
       </c>
       <c r="B32" t="n">
-        <v>79652</v>
+        <v>90598</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3794,41 +3789,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>376936</v>
+        <v>376967</v>
       </c>
       <c r="R32" t="n">
-        <v>6928683</v>
+        <v>6928836</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3858,6 +3853,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Bohål i högstubbe.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3872,22 +3872,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120460102</v>
+        <v>120460066</v>
       </c>
       <c r="B33" t="n">
-        <v>74654</v>
+        <v>78543</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3900,37 +3900,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>230405</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>377004</v>
+        <v>377009</v>
       </c>
       <c r="R33" t="n">
-        <v>6928780</v>
+        <v>6928804</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3974,22 +3974,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120460108</v>
+        <v>120460451</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4002,37 +4002,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>377042</v>
+        <v>377022</v>
       </c>
       <c r="R34" t="n">
-        <v>6928821</v>
+        <v>6928777</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4076,22 +4076,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120460958</v>
+        <v>120461047</v>
       </c>
       <c r="B35" t="n">
-        <v>90594</v>
+        <v>79624</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4104,21 +4104,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>376968</v>
+        <v>376936</v>
       </c>
       <c r="R35" t="n">
-        <v>6928679</v>
+        <v>6928683</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 38070-2024 artfynd.xlsx
+++ b/artfynd/A 38070-2024 artfynd.xlsx
@@ -2043,10 +2043,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120460059</v>
+        <v>120460931</v>
       </c>
       <c r="B15" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2055,25 +2055,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2083,13 +2083,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>376993</v>
+        <v>376983</v>
       </c>
       <c r="R15" t="n">
-        <v>6928790</v>
+        <v>6928691</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120461318</v>
+        <v>120460059</v>
       </c>
       <c r="B16" t="n">
-        <v>78543</v>
+        <v>57431</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2157,41 +2157,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>230405</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>376890</v>
+        <v>376993</v>
       </c>
       <c r="R16" t="n">
-        <v>6928691</v>
+        <v>6928790</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2235,22 +2235,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120460931</v>
+        <v>120461318</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>78543</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,16 +2263,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2283,17 +2283,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>376983</v>
+        <v>376890</v>
       </c>
       <c r="R17" t="n">
         <v>6928691</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2337,12 +2337,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120460235</v>
+        <v>120459943</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>77489</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3385,37 +3385,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>377043</v>
+        <v>377000</v>
       </c>
       <c r="R28" t="n">
-        <v>6928804</v>
+        <v>6928829</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3459,22 +3459,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120459943</v>
+        <v>120460235</v>
       </c>
       <c r="B29" t="n">
-        <v>77489</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>377000</v>
+        <v>377043</v>
       </c>
       <c r="R29" t="n">
-        <v>6928829</v>
+        <v>6928804</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3561,12 +3561,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 38070-2024 artfynd.xlsx
+++ b/artfynd/A 38070-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120315862</v>
+        <v>120459943</v>
       </c>
       <c r="B2" t="n">
-        <v>74670</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 38064-2024, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>377126</v>
+        <v>377000</v>
       </c>
       <c r="R2" t="n">
-        <v>6928838</v>
+        <v>6928829</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,34 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120315890</v>
+        <v>120460956</v>
       </c>
       <c r="B3" t="n">
-        <v>57486</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,46 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 38064-2024, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376945</v>
+        <v>376968</v>
       </c>
       <c r="R3" t="n">
-        <v>6928689</v>
+        <v>6928679</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,74 +857,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120315887</v>
+        <v>120460124</v>
       </c>
       <c r="B4" t="n">
-        <v>57444</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 38064-2024, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376945</v>
+        <v>377026</v>
       </c>
       <c r="R4" t="n">
-        <v>6928689</v>
+        <v>6928790</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,17 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Förekom i området under hela besöket</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120315882</v>
+        <v>120460909</v>
       </c>
       <c r="B5" t="n">
-        <v>79644</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,37 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 38064-2024, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>376978</v>
+        <v>376990</v>
       </c>
       <c r="R5" t="n">
-        <v>6928734</v>
+        <v>6928722</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,17 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flera fynd i området</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,34 +1045,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120459652</v>
+        <v>120461364</v>
       </c>
       <c r="B6" t="n">
-        <v>79672</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>376947</v>
+        <v>376857</v>
       </c>
       <c r="R6" t="n">
-        <v>6928818</v>
+        <v>6928677</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120461047</v>
+        <v>120460025</v>
       </c>
       <c r="B7" t="n">
-        <v>79672</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1267,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>376936</v>
+        <v>377000</v>
       </c>
       <c r="R7" t="n">
-        <v>6928683</v>
+        <v>6928813</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,19 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120460025</v>
+        <v>120460958</v>
       </c>
       <c r="B8" t="n">
-        <v>90684</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1369,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>377000</v>
+        <v>376968</v>
       </c>
       <c r="R8" t="n">
-        <v>6928813</v>
+        <v>6928679</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120459553</v>
+        <v>120315882</v>
       </c>
       <c r="B9" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1447,34 +1365,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>A 38064-2024, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>376934</v>
+        <v>376978</v>
       </c>
       <c r="R9" t="n">
-        <v>6928841</v>
+        <v>6928734</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,12 +1422,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Flera fynd i området</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1515,33 +1441,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120460124</v>
+        <v>120459652</v>
       </c>
       <c r="B10" t="n">
-        <v>90670</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1549,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>377026</v>
+        <v>376947</v>
       </c>
       <c r="R10" t="n">
-        <v>6928790</v>
+        <v>6928818</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,15 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120460909</v>
+        <v>120460504</v>
       </c>
       <c r="B11" t="n">
-        <v>90670</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,21 +1568,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1675,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>376990</v>
+        <v>377016</v>
       </c>
       <c r="R11" t="n">
-        <v>6928722</v>
+        <v>6928760</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,15 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120460637</v>
+        <v>120460548</v>
       </c>
       <c r="B12" t="n">
-        <v>79672</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,17 +1685,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>377053</v>
+        <v>377036</v>
       </c>
       <c r="R12" t="n">
-        <v>6928774</v>
+        <v>6928731</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1827,27 +1739,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120460454</v>
+        <v>120460591</v>
       </c>
       <c r="B13" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1855,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1879,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>377022</v>
+        <v>377037</v>
       </c>
       <c r="R13" t="n">
-        <v>6928777</v>
+        <v>6928708</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,15 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120460074</v>
+        <v>120460637</v>
       </c>
       <c r="B14" t="n">
-        <v>74698</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1957,37 +1859,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>376993</v>
+        <v>377053</v>
       </c>
       <c r="R14" t="n">
-        <v>6928790</v>
+        <v>6928774</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2031,12 +1933,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2046,12 +1948,7 @@
         <v>120460682</v>
       </c>
       <c r="B15" t="n">
-        <v>79672</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,12 +2045,7 @@
         <v>120460726</v>
       </c>
       <c r="B16" t="n">
-        <v>79672</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,15 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120460451</v>
+        <v>120460968</v>
       </c>
       <c r="B17" t="n">
-        <v>74698</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2263,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2287,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>377022</v>
+        <v>376968</v>
       </c>
       <c r="R17" t="n">
-        <v>6928777</v>
+        <v>6928679</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2349,15 +2236,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120460958</v>
+        <v>120461047</v>
       </c>
       <c r="B18" t="n">
-        <v>90684</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2365,21 +2247,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2389,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>376968</v>
+        <v>376936</v>
       </c>
       <c r="R18" t="n">
-        <v>6928679</v>
+        <v>6928683</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2451,37 +2333,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120460968</v>
+        <v>120459277</v>
       </c>
       <c r="B19" t="n">
-        <v>79672</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2491,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>376968</v>
+        <v>376949</v>
       </c>
       <c r="R19" t="n">
-        <v>6928679</v>
+        <v>6928868</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2553,37 +2430,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120459943</v>
+        <v>120459553</v>
       </c>
       <c r="B20" t="n">
-        <v>77537</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2593,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>377000</v>
+        <v>376934</v>
       </c>
       <c r="R20" t="n">
-        <v>6928829</v>
+        <v>6928841</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2655,53 +2527,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120460059</v>
+        <v>120459601</v>
       </c>
       <c r="B21" t="n">
-        <v>57455</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>376993</v>
+        <v>376916</v>
       </c>
       <c r="R21" t="n">
-        <v>6928790</v>
+        <v>6928831</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2745,31 +2612,26 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120459601</v>
+        <v>120459984</v>
       </c>
       <c r="B22" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2797,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>376916</v>
+        <v>376999</v>
       </c>
       <c r="R22" t="n">
-        <v>6928831</v>
+        <v>6928819</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -2859,53 +2721,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120460102</v>
+        <v>120460108</v>
       </c>
       <c r="B23" t="n">
-        <v>74698</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>377004</v>
+        <v>377042</v>
       </c>
       <c r="R23" t="n">
-        <v>6928780</v>
+        <v>6928821</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2949,65 +2806,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120460504</v>
+        <v>120460235</v>
       </c>
       <c r="B24" t="n">
-        <v>79672</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>377016</v>
+        <v>377043</v>
       </c>
       <c r="R24" t="n">
-        <v>6928760</v>
+        <v>6928804</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3051,31 +2903,26 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120459984</v>
+        <v>120460454</v>
       </c>
       <c r="B25" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3099,17 +2946,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>376999</v>
+        <v>377022</v>
       </c>
       <c r="R25" t="n">
-        <v>6928819</v>
+        <v>6928777</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3153,31 +3000,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120460108</v>
+        <v>120460931</v>
       </c>
       <c r="B26" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3201,17 +3043,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>377042</v>
+        <v>376983</v>
       </c>
       <c r="R26" t="n">
-        <v>6928821</v>
+        <v>6928691</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3255,65 +3097,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120460591</v>
+        <v>120464475</v>
       </c>
       <c r="B27" t="n">
-        <v>79672</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergvallen, Hjd</t>
+          <t>Lilltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>377037</v>
+        <v>376903</v>
       </c>
       <c r="R27" t="n">
-        <v>6928708</v>
+        <v>6928887</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3357,27 +3194,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120460569</v>
+        <v>120461333</v>
       </c>
       <c r="B28" t="n">
-        <v>79672</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3385,21 +3217,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3409,10 +3241,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>377036</v>
+        <v>376873</v>
       </c>
       <c r="R28" t="n">
-        <v>6928731</v>
+        <v>6928654</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3471,15 +3303,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120459810</v>
+        <v>120315862</v>
       </c>
       <c r="B29" t="n">
-        <v>90688</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3487,37 +3314,40 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>A 38064-2024, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>376967</v>
+        <v>377126</v>
       </c>
       <c r="R29" t="n">
-        <v>6928836</v>
+        <v>6928838</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3541,17 +3371,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Bohål i högstubbe.</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3560,33 +3385,29 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120460956</v>
+        <v>120459295</v>
       </c>
       <c r="B30" t="n">
-        <v>90958</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3594,21 +3415,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3618,10 +3439,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>376968</v>
+        <v>376949</v>
       </c>
       <c r="R30" t="n">
-        <v>6928679</v>
+        <v>6928868</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3680,37 +3501,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120461035</v>
+        <v>120459887</v>
       </c>
       <c r="B31" t="n">
-        <v>79700</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3720,10 +3536,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>376936</v>
+        <v>376970</v>
       </c>
       <c r="R31" t="n">
-        <v>6928683</v>
+        <v>6928854</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3782,15 +3598,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120460066</v>
+        <v>120460074</v>
       </c>
       <c r="B32" t="n">
-        <v>78591</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3798,37 +3609,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>230405</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>377009</v>
+        <v>376993</v>
       </c>
       <c r="R32" t="n">
-        <v>6928804</v>
+        <v>6928790</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3872,27 +3683,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120460235</v>
+        <v>120460102</v>
       </c>
       <c r="B33" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3900,37 +3706,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>377043</v>
+        <v>377004</v>
       </c>
       <c r="R33" t="n">
-        <v>6928804</v>
+        <v>6928780</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3974,27 +3780,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120460931</v>
+        <v>120460451</v>
       </c>
       <c r="B34" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4002,21 +3803,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4026,10 +3827,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>376983</v>
+        <v>377022</v>
       </c>
       <c r="R34" t="n">
-        <v>6928691</v>
+        <v>6928777</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4088,53 +3889,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120461318</v>
+        <v>120461035</v>
       </c>
       <c r="B35" t="n">
-        <v>78591</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>230405</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Hjd</t>
+          <t>Bergvallen, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>376890</v>
+        <v>376936</v>
       </c>
       <c r="R35" t="n">
-        <v>6928691</v>
+        <v>6928683</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4178,15 +3974,849 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120461329</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>376873</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6928654</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120315897</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>A 38064-2024, Hjd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>376875</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6928715</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Observerad under flera tillfällen under besöket</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120315903</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>A 38064-2024, Hjd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>376869</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6928711</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120315890</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>A 38064-2024, Hjd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>376945</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6928689</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120315887</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>A 38064-2024, Hjd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>376945</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6928689</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Förekom i området under hela besöket</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120460059</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Bergvallen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>376993</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6928790</v>
+      </c>
+      <c r="S41" t="n">
+        <v>20</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120460066</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>377009</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6928804</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
           <t>Håkan Thenander</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
+      <c r="AX42" t="inlineStr">
         <is>
           <t>Håkan Thenander</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120461318</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>376890</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6928691</v>
+      </c>
+      <c r="S43" t="n">
+        <v>4</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38070-2024 artfynd.xlsx
+++ b/artfynd/A 38070-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120459943</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460956</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460124</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460909</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120461364</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460958</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120315882</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120459652</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,6 +1701,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460504</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1748,6 +1803,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460548</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1845,6 +1905,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460591</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1942,6 +2007,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460637</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2039,6 +2109,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460682</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2136,6 +2211,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460726</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2233,6 +2313,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460968</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2330,6 +2415,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120461047</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2427,6 +2517,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120459277</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2524,6 +2619,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120459553</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2621,6 +2721,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120459601</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2718,6 +2823,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120459984</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2815,6 +2925,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460108</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2912,6 +3027,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460235</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3009,6 +3129,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460454</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3106,6 +3231,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460931</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3203,6 +3333,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120464475</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3300,6 +3435,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120461333</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3401,6 +3541,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120315862</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3498,6 +3643,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120459295</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3595,6 +3745,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120459887</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3692,6 +3847,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460074</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3789,6 +3949,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460102</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3886,6 +4051,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460451</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3983,6 +4153,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120461035</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4080,6 +4255,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120461329</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4198,6 +4378,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120315897</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4303,6 +4488,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120315903</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4412,6 +4602,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120315890</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4526,6 +4721,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120315887</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4623,6 +4823,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460059</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4720,6 +4925,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460066</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4817,8 +5027,57 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120461318</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>